--- a/upload/itens.xlsx
+++ b/upload/itens.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/upload/itens.xlsx
+++ b/upload/itens.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/upload/itens.xlsx
+++ b/upload/itens.xlsx
@@ -10320,7 +10320,7 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>PRC-22.032/2017-C</t>
+          <t>PRC-22.032/2017-B</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
@@ -10378,7 +10378,7 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>PRC-22.032/2017-D</t>
+          <t>PRC-22.032/2017-C</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
@@ -10436,7 +10436,7 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>PRC-22.032/2017-E</t>
+          <t>PRC-22.032/2017-D</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
@@ -10494,7 +10494,7 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>PRC-22.032/2017-B</t>
+          <t>PRC-22.032/2017-E</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
@@ -10726,7 +10726,7 @@
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>PRC-22.039/2017-E</t>
+          <t>PRC-22.039/2017-B</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
@@ -10784,7 +10784,7 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>PRC-22.039/2017-B</t>
+          <t>PRC-22.039/2017-E</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
@@ -12640,7 +12640,7 @@
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>PRC-22.013/2018-D</t>
+          <t>PRC-22.013/2018-B</t>
         </is>
       </c>
       <c r="E211" t="inlineStr">
@@ -12698,7 +12698,7 @@
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>PRC-22.013/2018-E</t>
+          <t>PRC-22.013/2018-C</t>
         </is>
       </c>
       <c r="E212" t="inlineStr">
@@ -12756,7 +12756,7 @@
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>PRC-22.013/2018-B</t>
+          <t>PRC-22.013/2018-D</t>
         </is>
       </c>
       <c r="E213" t="inlineStr">
@@ -12814,7 +12814,7 @@
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>PRC-22.013/2018-C</t>
+          <t>PRC-22.013/2018-E</t>
         </is>
       </c>
       <c r="E214" t="inlineStr">
@@ -13394,7 +13394,7 @@
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>PRC-22.023/2018-D</t>
+          <t>PRC-22.023/2018-B</t>
         </is>
       </c>
       <c r="E224" t="inlineStr">
@@ -13452,7 +13452,7 @@
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>PRC-22.023/2018-E</t>
+          <t>PRC-22.023/2018-C</t>
         </is>
       </c>
       <c r="E225" t="inlineStr">
@@ -13510,7 +13510,7 @@
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>PRC-22.023/2018-B</t>
+          <t>PRC-22.023/2018-D</t>
         </is>
       </c>
       <c r="E226" t="inlineStr">
@@ -13568,7 +13568,7 @@
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>PRC-22.023/2018-C</t>
+          <t>PRC-22.023/2018-E</t>
         </is>
       </c>
       <c r="E227" t="inlineStr">
@@ -22384,7 +22384,7 @@
       </c>
       <c r="D379" t="inlineStr">
         <is>
-          <t>DOV-002/2021-A</t>
+          <t>DOV-002/2021</t>
         </is>
       </c>
       <c r="E379" t="inlineStr">
@@ -22442,7 +22442,7 @@
       </c>
       <c r="D380" t="inlineStr">
         <is>
-          <t>DOV-002/2021</t>
+          <t>DOV-002/2021-A</t>
         </is>
       </c>
       <c r="E380" t="inlineStr">
@@ -26850,7 +26850,7 @@
       </c>
       <c r="D456" t="inlineStr">
         <is>
-          <t>DOV-001/2022-B</t>
+          <t>DOV-001/2022-A</t>
         </is>
       </c>
       <c r="E456" t="inlineStr">
@@ -26908,7 +26908,7 @@
       </c>
       <c r="D457" t="inlineStr">
         <is>
-          <t>DOV-001/2022-A</t>
+          <t>DOV-001/2022-B</t>
         </is>
       </c>
       <c r="E457" t="inlineStr">
@@ -27024,7 +27024,7 @@
       </c>
       <c r="D459" t="inlineStr">
         <is>
-          <t>DOV-001/2022-B</t>
+          <t>DOV-001/2022-A</t>
         </is>
       </c>
       <c r="E459" t="inlineStr">
@@ -27082,7 +27082,7 @@
       </c>
       <c r="D460" t="inlineStr">
         <is>
-          <t>DOV-001/2022-A</t>
+          <t>DOV-001/2022-B</t>
         </is>
       </c>
       <c r="E460" t="inlineStr">
@@ -32824,7 +32824,7 @@
       </c>
       <c r="D559" t="inlineStr">
         <is>
-          <t>DM-025/2023-B</t>
+          <t>DM-025/2023</t>
         </is>
       </c>
       <c r="E559" t="inlineStr">
@@ -32882,7 +32882,7 @@
       </c>
       <c r="D560" t="inlineStr">
         <is>
-          <t>DM-025/2023</t>
+          <t>DM-025/2023-B</t>
         </is>
       </c>
       <c r="E560" t="inlineStr">
@@ -32940,7 +32940,7 @@
       </c>
       <c r="D561" t="inlineStr">
         <is>
-          <t>DM-029/2023-B</t>
+          <t>DM-029/2023</t>
         </is>
       </c>
       <c r="E561" t="inlineStr">
@@ -33056,7 +33056,7 @@
       </c>
       <c r="D563" t="inlineStr">
         <is>
-          <t>DM-029/2023</t>
+          <t>DM-029/2023-B</t>
         </is>
       </c>
       <c r="E563" t="inlineStr">
@@ -39842,7 +39842,7 @@
       </c>
       <c r="D680" t="inlineStr">
         <is>
-          <t>DM-012/2024-A</t>
+          <t>DM-012/2024</t>
         </is>
       </c>
       <c r="E680" t="inlineStr">
@@ -39900,7 +39900,7 @@
       </c>
       <c r="D681" t="inlineStr">
         <is>
-          <t>DM-012/2024</t>
+          <t>DM-012/2024-A</t>
         </is>
       </c>
       <c r="E681" t="inlineStr">
@@ -41872,7 +41872,7 @@
       </c>
       <c r="D715" t="inlineStr">
         <is>
-          <t>DM-001/2022</t>
+          <t>DC-9472756/2025</t>
         </is>
       </c>
       <c r="E715" t="inlineStr">
@@ -41930,7 +41930,7 @@
       </c>
       <c r="D716" t="inlineStr">
         <is>
-          <t>DC-9472756/2025</t>
+          <t>DM-001/2022</t>
         </is>
       </c>
       <c r="E716" t="inlineStr">
@@ -42104,7 +42104,7 @@
       </c>
       <c r="D719" t="inlineStr">
         <is>
-          <t>DM-001/2021</t>
+          <t>DC-9472752/2025</t>
         </is>
       </c>
       <c r="E719" t="inlineStr">
@@ -42162,7 +42162,7 @@
       </c>
       <c r="D720" t="inlineStr">
         <is>
-          <t>DC-9472752/2025</t>
+          <t>DM-001/2021</t>
         </is>
       </c>
       <c r="E720" t="inlineStr">
@@ -42916,7 +42916,7 @@
       </c>
       <c r="D733" t="inlineStr">
         <is>
-          <t>DC-9498666/2026</t>
+          <t>DC-9453556/2025</t>
         </is>
       </c>
       <c r="E733" t="inlineStr">
@@ -42974,7 +42974,7 @@
       </c>
       <c r="D734" t="inlineStr">
         <is>
-          <t>DC-9453556/2025</t>
+          <t>DC-9498666/2026</t>
         </is>
       </c>
       <c r="E734" t="inlineStr">

--- a/upload/itens.xlsx
+++ b/upload/itens.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P799"/>
+  <dimension ref="A1:P806"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -45806,22 +45806,22 @@
       </c>
       <c r="B783" t="inlineStr">
         <is>
-          <t>1301606 000003/2025</t>
+          <t>1301606 000002/2026</t>
         </is>
       </c>
       <c r="C783" t="inlineStr">
         <is>
-          <t>9497471</t>
+          <t>9507997</t>
         </is>
       </c>
       <c r="D783" t="inlineStr">
         <is>
-          <t>DC-9497471/2026</t>
+          <t>DC-9507997/2026</t>
         </is>
       </c>
       <c r="E783" t="inlineStr">
         <is>
-          <t>CONSTRUTORA ITUSANE DE ITURAMA LTDA</t>
+          <t>OPACO ENGENHARIA LTDA</t>
         </is>
       </c>
       <c r="F783" t="n">
@@ -45849,13 +45849,13 @@
         <v>1</v>
       </c>
       <c r="N783" t="n">
-        <v>4383662.29</v>
+        <v>28204745.51</v>
       </c>
       <c r="O783" t="n">
-        <v>4383662.29</v>
+        <v>28204745.51</v>
       </c>
       <c r="P783" t="n">
-        <v>3700000</v>
+        <v>28204745.51</v>
       </c>
     </row>
     <row r="784">
@@ -45864,22 +45864,22 @@
       </c>
       <c r="B784" t="inlineStr">
         <is>
-          <t>2301520 000010/2026</t>
+          <t>1301606 000003/2025</t>
         </is>
       </c>
       <c r="C784" t="inlineStr">
         <is>
-          <t>9498942</t>
+          <t>9497471</t>
         </is>
       </c>
       <c r="D784" t="inlineStr">
         <is>
-          <t>DC-011R/2024</t>
+          <t>DC-9497471/2026</t>
         </is>
       </c>
       <c r="E784" t="inlineStr">
         <is>
-          <t>HWN ENGENHARIA LTDA</t>
+          <t>CONSTRUTORA ITUSANE DE ITURAMA LTDA</t>
         </is>
       </c>
       <c r="F784" t="n">
@@ -45907,13 +45907,13 @@
         <v>1</v>
       </c>
       <c r="N784" t="n">
-        <v>2962697.76</v>
+        <v>4383662.29</v>
       </c>
       <c r="O784" t="n">
-        <v>2962697.76</v>
+        <v>4383662.29</v>
       </c>
       <c r="P784" t="n">
-        <v>2962697.76</v>
+        <v>3700000</v>
       </c>
     </row>
     <row r="785">
@@ -45922,22 +45922,22 @@
       </c>
       <c r="B785" t="inlineStr">
         <is>
-          <t>2301520 000030/2025</t>
+          <t>2301520 000001/2026</t>
         </is>
       </c>
       <c r="C785" t="inlineStr">
         <is>
-          <t>9495596</t>
+          <t>9511902</t>
         </is>
       </c>
       <c r="D785" t="inlineStr">
         <is>
-          <t>DC-9495596/2026</t>
+          <t>DC-9511902/2026</t>
         </is>
       </c>
       <c r="E785" t="inlineStr">
         <is>
-          <t>S3 CONSTRUTORA LTDA - ME</t>
+          <t>LCM CONSTRUCAO E COMERCIO S.A</t>
         </is>
       </c>
       <c r="F785" t="n">
@@ -45962,16 +45962,16 @@
         </is>
       </c>
       <c r="M785" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="N785" t="n">
-        <v>15970367.44</v>
+        <v>19733859.27</v>
       </c>
       <c r="O785" t="n">
-        <v>15970367.44</v>
+        <v>19733859.26</v>
       </c>
       <c r="P785" t="n">
-        <v>12246077.75</v>
+        <v>16179998.72</v>
       </c>
     </row>
     <row r="786">
@@ -45980,56 +45980,56 @@
       </c>
       <c r="B786" t="inlineStr">
         <is>
-          <t>2301520 000034/2025</t>
+          <t>2301520 000005/2026</t>
         </is>
       </c>
       <c r="C786" t="inlineStr">
         <is>
-          <t>9493122</t>
+          <t>9515457</t>
         </is>
       </c>
       <c r="D786" t="inlineStr">
         <is>
-          <t>DC-9493122/2026</t>
+          <t>DC-9515457/2026</t>
         </is>
       </c>
       <c r="E786" t="inlineStr">
         <is>
-          <t>MAIA MELO ENGENHARIA LTDA</t>
+          <t>HWN ENGENHARIA LTDA</t>
         </is>
       </c>
       <c r="F786" t="n">
         <v>1</v>
       </c>
       <c r="G786" t="n">
-        <v>11207</v>
+        <v>1740</v>
       </c>
       <c r="H786" t="inlineStr">
         <is>
-          <t>SERVICOS DE SUPERVISAO DE OBRAS E SERVICOS DO SISTEMA VIARIO</t>
+          <t>SERVICOS DE IMPLANTACAO E PAVIMENTACAO ASFALTICA</t>
         </is>
       </c>
       <c r="I786" t="inlineStr"/>
       <c r="J786" t="inlineStr"/>
       <c r="K786" t="n">
-        <v>3951</v>
+        <v>5107</v>
       </c>
       <c r="L786" t="inlineStr">
         <is>
-          <t>SERVICOS DE GERENCIAMENTO, SUPERVISAO E FISCALIZACAO DE OBRAS</t>
+          <t>EXECUCAO DE OBRAS POR CONTRATO DE BENS NAO PATRIMONIAVEIS</t>
         </is>
       </c>
       <c r="M786" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N786" t="n">
-        <v>7420078.73</v>
+        <v>120767701.47</v>
       </c>
       <c r="O786" t="n">
-        <v>7420078.73</v>
+        <v>120767701.47</v>
       </c>
       <c r="P786" t="n">
-        <v>6677404.33</v>
+        <v>87996201.20999999</v>
       </c>
     </row>
     <row r="787">
@@ -46038,56 +46038,56 @@
       </c>
       <c r="B787" t="inlineStr">
         <is>
-          <t>2301520 000035/2025</t>
+          <t>2301520 000010/2026</t>
         </is>
       </c>
       <c r="C787" t="inlineStr">
         <is>
-          <t>9492715</t>
+          <t>9498942</t>
         </is>
       </c>
       <c r="D787" t="inlineStr">
         <is>
-          <t>DC-9492715/2025</t>
+          <t>DC-011R/2024</t>
         </is>
       </c>
       <c r="E787" t="inlineStr">
         <is>
-          <t>MAIA MELO ENGENHARIA LTDA</t>
+          <t>HWN ENGENHARIA LTDA</t>
         </is>
       </c>
       <c r="F787" t="n">
         <v>1</v>
       </c>
       <c r="G787" t="n">
-        <v>11207</v>
+        <v>1740</v>
       </c>
       <c r="H787" t="inlineStr">
         <is>
-          <t>SERVICOS DE SUPERVISAO DE OBRAS E SERVICOS DO SISTEMA VIARIO</t>
+          <t>SERVICOS DE IMPLANTACAO E PAVIMENTACAO ASFALTICA</t>
         </is>
       </c>
       <c r="I787" t="inlineStr"/>
       <c r="J787" t="inlineStr"/>
       <c r="K787" t="n">
-        <v>3951</v>
+        <v>5107</v>
       </c>
       <c r="L787" t="inlineStr">
         <is>
-          <t>SERVICOS DE GERENCIAMENTO, SUPERVISAO E FISCALIZACAO DE OBRAS</t>
+          <t>EXECUCAO DE OBRAS POR CONTRATO DE BENS NAO PATRIMONIAVEIS</t>
         </is>
       </c>
       <c r="M787" t="n">
         <v>1</v>
       </c>
       <c r="N787" t="n">
-        <v>3563439</v>
+        <v>2962697.76</v>
       </c>
       <c r="O787" t="n">
-        <v>3563439</v>
+        <v>2962697.76</v>
       </c>
       <c r="P787" t="n">
-        <v>3028048.96</v>
+        <v>2962697.76</v>
       </c>
     </row>
     <row r="788">
@@ -46096,22 +46096,22 @@
       </c>
       <c r="B788" t="inlineStr">
         <is>
-          <t>2301520 000036/2025</t>
+          <t>2301520 000030/2025</t>
         </is>
       </c>
       <c r="C788" t="inlineStr">
         <is>
-          <t>9493529</t>
+          <t>9495596</t>
         </is>
       </c>
       <c r="D788" t="inlineStr">
         <is>
-          <t>DC-9493529/2026</t>
+          <t>DC-9495596/2026</t>
         </is>
       </c>
       <c r="E788" t="inlineStr">
         <is>
-          <t>CONSTRUTORA CONTORNO LTDA</t>
+          <t>S3 CONSTRUTORA LTDA - ME</t>
         </is>
       </c>
       <c r="F788" t="n">
@@ -46139,13 +46139,13 @@
         <v>1</v>
       </c>
       <c r="N788" t="n">
-        <v>44004328.59</v>
+        <v>15970367.44</v>
       </c>
       <c r="O788" t="n">
-        <v>44004328.59</v>
+        <v>15970367.44</v>
       </c>
       <c r="P788" t="n">
-        <v>37600000</v>
+        <v>12246077.75</v>
       </c>
     </row>
     <row r="789">
@@ -46154,56 +46154,56 @@
       </c>
       <c r="B789" t="inlineStr">
         <is>
-          <t>2301520 000037/2025</t>
+          <t>2301520 000034/2025</t>
         </is>
       </c>
       <c r="C789" t="inlineStr">
         <is>
-          <t>9501601</t>
+          <t>9493122</t>
         </is>
       </c>
       <c r="D789" t="inlineStr">
         <is>
-          <t>DC-9501601/2026</t>
+          <t>DC-9493122/2026</t>
         </is>
       </c>
       <c r="E789" t="inlineStr">
         <is>
-          <t>S3 CONSTRUTORA LTDA - ME</t>
+          <t>MAIA MELO ENGENHARIA LTDA</t>
         </is>
       </c>
       <c r="F789" t="n">
         <v>1</v>
       </c>
       <c r="G789" t="n">
-        <v>1740</v>
+        <v>11207</v>
       </c>
       <c r="H789" t="inlineStr">
         <is>
-          <t>SERVICOS DE IMPLANTACAO E PAVIMENTACAO ASFALTICA</t>
+          <t>SERVICOS DE SUPERVISAO DE OBRAS E SERVICOS DO SISTEMA VIARIO</t>
         </is>
       </c>
       <c r="I789" t="inlineStr"/>
       <c r="J789" t="inlineStr"/>
       <c r="K789" t="n">
-        <v>5107</v>
+        <v>3951</v>
       </c>
       <c r="L789" t="inlineStr">
         <is>
-          <t>EXECUCAO DE OBRAS POR CONTRATO DE BENS NAO PATRIMONIAVEIS</t>
+          <t>SERVICOS DE GERENCIAMENTO, SUPERVISAO E FISCALIZACAO DE OBRAS</t>
         </is>
       </c>
       <c r="M789" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N789" t="n">
-        <v>11144418.23</v>
+        <v>7420078.73</v>
       </c>
       <c r="O789" t="n">
-        <v>11144418.22</v>
+        <v>7420078.73</v>
       </c>
       <c r="P789" t="n">
-        <v>9814000</v>
+        <v>6677404.33</v>
       </c>
     </row>
     <row r="790">
@@ -46212,56 +46212,56 @@
       </c>
       <c r="B790" t="inlineStr">
         <is>
-          <t>2301520 000044/2025</t>
+          <t>2301520 000035/2025</t>
         </is>
       </c>
       <c r="C790" t="inlineStr">
         <is>
-          <t>9505062</t>
+          <t>9492715</t>
         </is>
       </c>
       <c r="D790" t="inlineStr">
         <is>
-          <t>DC-9505062/2026</t>
+          <t>DC-9492715/2025</t>
         </is>
       </c>
       <c r="E790" t="inlineStr">
         <is>
-          <t>S3 CONSTRUTORA LTDA - ME</t>
+          <t>MAIA MELO ENGENHARIA LTDA</t>
         </is>
       </c>
       <c r="F790" t="n">
         <v>1</v>
       </c>
       <c r="G790" t="n">
-        <v>1740</v>
+        <v>11207</v>
       </c>
       <c r="H790" t="inlineStr">
         <is>
-          <t>SERVICOS DE IMPLANTACAO E PAVIMENTACAO ASFALTICA</t>
+          <t>SERVICOS DE SUPERVISAO DE OBRAS E SERVICOS DO SISTEMA VIARIO</t>
         </is>
       </c>
       <c r="I790" t="inlineStr"/>
       <c r="J790" t="inlineStr"/>
       <c r="K790" t="n">
-        <v>5107</v>
+        <v>3951</v>
       </c>
       <c r="L790" t="inlineStr">
         <is>
-          <t>EXECUCAO DE OBRAS POR CONTRATO DE BENS NAO PATRIMONIAVEIS</t>
+          <t>SERVICOS DE GERENCIAMENTO, SUPERVISAO E FISCALIZACAO DE OBRAS</t>
         </is>
       </c>
       <c r="M790" t="n">
         <v>1</v>
       </c>
       <c r="N790" t="n">
-        <v>3965005.14</v>
+        <v>3563439</v>
       </c>
       <c r="O790" t="n">
-        <v>3965005.14</v>
+        <v>3563439</v>
       </c>
       <c r="P790" t="n">
-        <v>2961858.83</v>
+        <v>3028048.96</v>
       </c>
     </row>
     <row r="791">
@@ -46270,56 +46270,56 @@
       </c>
       <c r="B791" t="inlineStr">
         <is>
-          <t>2301617 000003/2025</t>
+          <t>2301520 000036/2025</t>
         </is>
       </c>
       <c r="C791" t="inlineStr">
         <is>
-          <t>9499286</t>
+          <t>9493529</t>
         </is>
       </c>
       <c r="D791" t="inlineStr">
         <is>
-          <t>AMA-9499286/2026</t>
+          <t>DC-9493529/2026</t>
         </is>
       </c>
       <c r="E791" t="inlineStr">
         <is>
-          <t>STE SERVICOS TECNICOS DE ENGENHARIA SA</t>
+          <t>CONSTRUTORA CONTORNO LTDA</t>
         </is>
       </c>
       <c r="F791" t="n">
         <v>1</v>
       </c>
       <c r="G791" t="n">
-        <v>115827</v>
+        <v>1740</v>
       </c>
       <c r="H791" t="inlineStr">
         <is>
-          <t xml:space="preserve">SERVICOS TECNICOS EM AREA AMBIENTAL </t>
+          <t>SERVICOS DE IMPLANTACAO E PAVIMENTACAO ASFALTICA</t>
         </is>
       </c>
       <c r="I791" t="inlineStr"/>
       <c r="J791" t="inlineStr"/>
       <c r="K791" t="n">
-        <v>3973</v>
+        <v>5107</v>
       </c>
       <c r="L791" t="inlineStr">
         <is>
-          <t>SERVICO DE ENGENHARIA PARA OPERACAO DE BENS DE DOMINIO PUBLICO</t>
+          <t>EXECUCAO DE OBRAS POR CONTRATO DE BENS NAO PATRIMONIAVEIS</t>
         </is>
       </c>
       <c r="M791" t="n">
         <v>1</v>
       </c>
       <c r="N791" t="n">
-        <v>48044257.29</v>
+        <v>44004328.59</v>
       </c>
       <c r="O791" t="n">
-        <v>48044257.29</v>
+        <v>44004328.59</v>
       </c>
       <c r="P791" t="n">
-        <v>36033198.22</v>
+        <v>37600000</v>
       </c>
     </row>
     <row r="792">
@@ -46328,33 +46328,33 @@
       </c>
       <c r="B792" t="inlineStr">
         <is>
-          <t>2301762 000001/2025</t>
+          <t>2301520 000037/2025</t>
         </is>
       </c>
       <c r="C792" t="inlineStr">
         <is>
-          <t>9493180</t>
+          <t>9501601</t>
         </is>
       </c>
       <c r="D792" t="inlineStr">
         <is>
-          <t>DM-9493180/2026</t>
+          <t>DC-9501601/2026</t>
         </is>
       </c>
       <c r="E792" t="inlineStr">
         <is>
-          <t>CONSTRUTORA SAGENDRA LTDA</t>
+          <t>S3 CONSTRUTORA LTDA - ME</t>
         </is>
       </c>
       <c r="F792" t="n">
         <v>1</v>
       </c>
       <c r="G792" t="n">
-        <v>1872</v>
+        <v>1740</v>
       </c>
       <c r="H792" t="inlineStr">
         <is>
-          <t>SERVICOS DE RECUPERACAO DE RODOVIAS</t>
+          <t>SERVICOS DE IMPLANTACAO E PAVIMENTACAO ASFALTICA</t>
         </is>
       </c>
       <c r="I792" t="inlineStr"/>
@@ -46368,16 +46368,16 @@
         </is>
       </c>
       <c r="M792" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N792" t="n">
-        <v>99982008.22</v>
+        <v>11144418.23</v>
       </c>
       <c r="O792" t="n">
-        <v>99982008.22</v>
+        <v>11144418.22</v>
       </c>
       <c r="P792" t="n">
-        <v>64984305.34</v>
+        <v>9814000</v>
       </c>
     </row>
     <row r="793">
@@ -46386,33 +46386,33 @@
       </c>
       <c r="B793" t="inlineStr">
         <is>
-          <t>2301762 000022/2025</t>
+          <t>2301520 000044/2025</t>
         </is>
       </c>
       <c r="C793" t="inlineStr">
         <is>
-          <t>9493137</t>
+          <t>9505062</t>
         </is>
       </c>
       <c r="D793" t="inlineStr">
         <is>
-          <t>DM-9493137/2026</t>
+          <t>DC-9505062/2026</t>
         </is>
       </c>
       <c r="E793" t="inlineStr">
         <is>
-          <t>CONSTRUTORA ITAMARACA LTDA</t>
+          <t>S3 CONSTRUTORA LTDA - ME</t>
         </is>
       </c>
       <c r="F793" t="n">
         <v>1</v>
       </c>
       <c r="G793" t="n">
-        <v>1872</v>
+        <v>1740</v>
       </c>
       <c r="H793" t="inlineStr">
         <is>
-          <t>SERVICOS DE RECUPERACAO DE RODOVIAS</t>
+          <t>SERVICOS DE IMPLANTACAO E PAVIMENTACAO ASFALTICA</t>
         </is>
       </c>
       <c r="I793" t="inlineStr"/>
@@ -46429,13 +46429,13 @@
         <v>1</v>
       </c>
       <c r="N793" t="n">
-        <v>11437822.96</v>
+        <v>3965005.14</v>
       </c>
       <c r="O793" t="n">
-        <v>11437822.96</v>
+        <v>3965005.14</v>
       </c>
       <c r="P793" t="n">
-        <v>10619818.83</v>
+        <v>2961858.83</v>
       </c>
     </row>
     <row r="794">
@@ -46444,56 +46444,56 @@
       </c>
       <c r="B794" t="inlineStr">
         <is>
-          <t>2301762 000023/2025</t>
+          <t>2301617 000003/2025</t>
         </is>
       </c>
       <c r="C794" t="inlineStr">
         <is>
-          <t>9497685</t>
+          <t>9499286</t>
         </is>
       </c>
       <c r="D794" t="inlineStr">
         <is>
-          <t>DM-9497685/2026</t>
+          <t>AMA-9499286/2026</t>
         </is>
       </c>
       <c r="E794" t="inlineStr">
         <is>
-          <t>LCM CONSTRUCAO E COMERCIO S.A</t>
+          <t>STE SERVICOS TECNICOS DE ENGENHARIA SA</t>
         </is>
       </c>
       <c r="F794" t="n">
         <v>1</v>
       </c>
       <c r="G794" t="n">
-        <v>1872</v>
+        <v>115827</v>
       </c>
       <c r="H794" t="inlineStr">
         <is>
-          <t>SERVICOS DE RECUPERACAO DE RODOVIAS</t>
+          <t xml:space="preserve">SERVICOS TECNICOS EM AREA AMBIENTAL </t>
         </is>
       </c>
       <c r="I794" t="inlineStr"/>
       <c r="J794" t="inlineStr"/>
       <c r="K794" t="n">
-        <v>5107</v>
+        <v>3973</v>
       </c>
       <c r="L794" t="inlineStr">
         <is>
-          <t>EXECUCAO DE OBRAS POR CONTRATO DE BENS NAO PATRIMONIAVEIS</t>
+          <t>SERVICO DE ENGENHARIA PARA OPERACAO DE BENS DE DOMINIO PUBLICO</t>
         </is>
       </c>
       <c r="M794" t="n">
         <v>1</v>
       </c>
       <c r="N794" t="n">
-        <v>19019690.63</v>
+        <v>48044257.29</v>
       </c>
       <c r="O794" t="n">
-        <v>19019690.63</v>
+        <v>48044257.29</v>
       </c>
       <c r="P794" t="n">
-        <v>14264750.82</v>
+        <v>36033198.22</v>
       </c>
     </row>
     <row r="795">
@@ -46502,56 +46502,56 @@
       </c>
       <c r="B795" t="inlineStr">
         <is>
-          <t>2301762 000025/2025</t>
+          <t>2301617 000004/2025</t>
         </is>
       </c>
       <c r="C795" t="inlineStr">
         <is>
-          <t>9493202</t>
+          <t>9502187</t>
         </is>
       </c>
       <c r="D795" t="inlineStr">
         <is>
-          <t>DM-9493202/2026</t>
+          <t xml:space="preserve">  AMA-9502187/2026</t>
         </is>
       </c>
       <c r="E795" t="inlineStr">
         <is>
-          <t>AGR BOTELHO ENGENHARIA LTDA</t>
+          <t>E+ ENGENHARIA E MEIO AMBIENTE LTDA</t>
         </is>
       </c>
       <c r="F795" t="n">
         <v>1</v>
       </c>
       <c r="G795" t="n">
-        <v>1872</v>
+        <v>23167</v>
       </c>
       <c r="H795" t="inlineStr">
         <is>
-          <t>SERVICOS DE RECUPERACAO DE RODOVIAS</t>
+          <t>SERVICOS TECNICOS  ESPECIALIZADOS  EM ELABORACAO DE PROJETOSEXECUTIVOS</t>
         </is>
       </c>
       <c r="I795" t="inlineStr"/>
       <c r="J795" t="inlineStr"/>
       <c r="K795" t="n">
-        <v>5107</v>
+        <v>3999</v>
       </c>
       <c r="L795" t="inlineStr">
         <is>
-          <t>EXECUCAO DE OBRAS POR CONTRATO DE BENS NAO PATRIMONIAVEIS</t>
+          <t>OUTROS SERVICOS PESSOA JURIDICA</t>
         </is>
       </c>
       <c r="M795" t="n">
         <v>1</v>
       </c>
       <c r="N795" t="n">
-        <v>6305546.68</v>
+        <v>1904028.2</v>
       </c>
       <c r="O795" t="n">
-        <v>6305546.68</v>
+        <v>1904028.2</v>
       </c>
       <c r="P795" t="n">
-        <v>4557819.64</v>
+        <v>1768342.65</v>
       </c>
     </row>
     <row r="796">
@@ -46560,56 +46560,56 @@
       </c>
       <c r="B796" t="inlineStr">
         <is>
-          <t>2301762 000026/2025</t>
+          <t>2301762 000001/2025</t>
         </is>
       </c>
       <c r="C796" t="inlineStr">
         <is>
-          <t>9502116</t>
+          <t>9493180</t>
         </is>
       </c>
       <c r="D796" t="inlineStr">
         <is>
-          <t>DM-9502116/2026</t>
+          <t>DM-9493180/2026</t>
         </is>
       </c>
       <c r="E796" t="inlineStr">
         <is>
-          <t>PLANEP PLANEJAMENTO ESTUDOS E PROJETOS LTDA</t>
+          <t>CONSTRUTORA SAGENDRA LTDA</t>
         </is>
       </c>
       <c r="F796" t="n">
         <v>1</v>
       </c>
       <c r="G796" t="n">
-        <v>8125</v>
+        <v>1872</v>
       </c>
       <c r="H796" t="inlineStr">
         <is>
-          <t>SERVICOS DE CONSULTORIA EM AREA DE ENGENHARIA CIVIL</t>
+          <t>SERVICOS DE RECUPERACAO DE RODOVIAS</t>
         </is>
       </c>
       <c r="I796" t="inlineStr"/>
       <c r="J796" t="inlineStr"/>
       <c r="K796" t="n">
-        <v>3951</v>
+        <v>5107</v>
       </c>
       <c r="L796" t="inlineStr">
         <is>
-          <t>SERVICOS DE GERENCIAMENTO, SUPERVISAO E FISCALIZACAO DE OBRAS</t>
+          <t>EXECUCAO DE OBRAS POR CONTRATO DE BENS NAO PATRIMONIAVEIS</t>
         </is>
       </c>
       <c r="M796" t="n">
         <v>1</v>
       </c>
       <c r="N796" t="n">
-        <v>8281446.48</v>
+        <v>99982008.22</v>
       </c>
       <c r="O796" t="n">
-        <v>0</v>
+        <v>99982008.22</v>
       </c>
       <c r="P796" t="n">
-        <v>0</v>
+        <v>64984305.34</v>
       </c>
     </row>
     <row r="797">
@@ -46618,56 +46618,56 @@
       </c>
       <c r="B797" t="inlineStr">
         <is>
-          <t>2301762 000026/2025</t>
+          <t>2301762 000001/2026</t>
         </is>
       </c>
       <c r="C797" t="inlineStr">
         <is>
-          <t>9502116</t>
+          <t>9512044</t>
         </is>
       </c>
       <c r="D797" t="inlineStr">
         <is>
-          <t>DM-9502116/2026</t>
+          <t>DM-9512044/2026</t>
         </is>
       </c>
       <c r="E797" t="inlineStr">
         <is>
-          <t>PLANEP PLANEJAMENTO ESTUDOS E PROJETOS LTDA</t>
+          <t>HWN ENGENHARIA LTDA</t>
         </is>
       </c>
       <c r="F797" t="n">
         <v>1</v>
       </c>
       <c r="G797" t="n">
-        <v>8125</v>
+        <v>1872</v>
       </c>
       <c r="H797" t="inlineStr">
         <is>
-          <t>SERVICOS DE CONSULTORIA EM AREA DE ENGENHARIA CIVIL</t>
+          <t>SERVICOS DE RECUPERACAO DE RODOVIAS</t>
         </is>
       </c>
       <c r="I797" t="inlineStr"/>
       <c r="J797" t="inlineStr"/>
       <c r="K797" t="n">
-        <v>5106</v>
+        <v>5107</v>
       </c>
       <c r="L797" t="inlineStr">
         <is>
-          <t>ESTUDOS E PROJETOS DE BENS NAO PATRIMONIAVEIS</t>
+          <t>EXECUCAO DE OBRAS POR CONTRATO DE BENS NAO PATRIMONIAVEIS</t>
         </is>
       </c>
       <c r="M797" t="n">
         <v>1</v>
       </c>
       <c r="N797" t="n">
-        <v>8281446.48</v>
+        <v>13602005.38</v>
       </c>
       <c r="O797" t="n">
-        <v>8281446.48</v>
+        <v>13602005.38</v>
       </c>
       <c r="P797" t="n">
-        <v>5342582.88</v>
+        <v>11358610.11</v>
       </c>
     </row>
     <row r="798">
@@ -46676,22 +46676,22 @@
       </c>
       <c r="B798" t="inlineStr">
         <is>
-          <t>2301762 000030/2025</t>
+          <t>2301762 000004/2026</t>
         </is>
       </c>
       <c r="C798" t="inlineStr">
         <is>
-          <t>9504058</t>
+          <t>9512043</t>
         </is>
       </c>
       <c r="D798" t="inlineStr">
         <is>
-          <t>DM-9504058/2026</t>
+          <t>DM-9512043/2026</t>
         </is>
       </c>
       <c r="E798" t="inlineStr">
         <is>
-          <t>EMCONBRAS EMPRESA DE CONSERVACAO BRASILEIRA LTDA</t>
+          <t>LOMAE MAQUINAS E EMPREENDIMENTOS LTDA</t>
         </is>
       </c>
       <c r="F798" t="n">
@@ -46719,13 +46719,13 @@
         <v>1</v>
       </c>
       <c r="N798" t="n">
-        <v>28640371.76</v>
+        <v>73340224.20999999</v>
       </c>
       <c r="O798" t="n">
-        <v>28640371.76</v>
+        <v>73340224.20999999</v>
       </c>
       <c r="P798" t="n">
-        <v>19798000</v>
+        <v>44002130</v>
       </c>
     </row>
     <row r="799">
@@ -46734,55 +46734,461 @@
       </c>
       <c r="B799" t="inlineStr">
         <is>
-          <t>2301901 000001/2025</t>
+          <t>2301762 000022/2025</t>
         </is>
       </c>
       <c r="C799" t="inlineStr">
         <is>
-          <t>9493205</t>
+          <t>9493137</t>
         </is>
       </c>
       <c r="D799" t="inlineStr">
         <is>
-          <t>DO-9493205/2026-L4</t>
+          <t>DM-9493137/2026</t>
         </is>
       </c>
       <c r="E799" t="inlineStr">
         <is>
-          <t>FOCALLE - ENGENHARIA VIARIA LTDA.</t>
+          <t>CONSTRUTORA ITAMARACA LTDA</t>
         </is>
       </c>
       <c r="F799" t="n">
         <v>1</v>
       </c>
       <c r="G799" t="n">
-        <v>66419</v>
+        <v>1872</v>
       </c>
       <c r="H799" t="inlineStr">
         <is>
-          <t>SERVICO DE VIGILANCIA ELETRONICA DE TRANSITO E TRAFEGO E    TRATAMENTO DAS IMAGENS</t>
+          <t>SERVICOS DE RECUPERACAO DE RODOVIAS</t>
         </is>
       </c>
       <c r="I799" t="inlineStr"/>
       <c r="J799" t="inlineStr"/>
       <c r="K799" t="n">
+        <v>5107</v>
+      </c>
+      <c r="L799" t="inlineStr">
+        <is>
+          <t>EXECUCAO DE OBRAS POR CONTRATO DE BENS NAO PATRIMONIAVEIS</t>
+        </is>
+      </c>
+      <c r="M799" t="n">
+        <v>1</v>
+      </c>
+      <c r="N799" t="n">
+        <v>11437822.96</v>
+      </c>
+      <c r="O799" t="n">
+        <v>11437822.96</v>
+      </c>
+      <c r="P799" t="n">
+        <v>10619818.83</v>
+      </c>
+    </row>
+    <row r="800">
+      <c r="A800" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B800" t="inlineStr">
+        <is>
+          <t>2301762 000023/2025</t>
+        </is>
+      </c>
+      <c r="C800" t="inlineStr">
+        <is>
+          <t>9497685</t>
+        </is>
+      </c>
+      <c r="D800" t="inlineStr">
+        <is>
+          <t>DM-9497685/2026</t>
+        </is>
+      </c>
+      <c r="E800" t="inlineStr">
+        <is>
+          <t>LCM CONSTRUCAO E COMERCIO S.A</t>
+        </is>
+      </c>
+      <c r="F800" t="n">
+        <v>1</v>
+      </c>
+      <c r="G800" t="n">
+        <v>1872</v>
+      </c>
+      <c r="H800" t="inlineStr">
+        <is>
+          <t>SERVICOS DE RECUPERACAO DE RODOVIAS</t>
+        </is>
+      </c>
+      <c r="I800" t="inlineStr"/>
+      <c r="J800" t="inlineStr"/>
+      <c r="K800" t="n">
+        <v>5107</v>
+      </c>
+      <c r="L800" t="inlineStr">
+        <is>
+          <t>EXECUCAO DE OBRAS POR CONTRATO DE BENS NAO PATRIMONIAVEIS</t>
+        </is>
+      </c>
+      <c r="M800" t="n">
+        <v>1</v>
+      </c>
+      <c r="N800" t="n">
+        <v>19019690.63</v>
+      </c>
+      <c r="O800" t="n">
+        <v>19019690.63</v>
+      </c>
+      <c r="P800" t="n">
+        <v>14264750.82</v>
+      </c>
+    </row>
+    <row r="801">
+      <c r="A801" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B801" t="inlineStr">
+        <is>
+          <t>2301762 000025/2025</t>
+        </is>
+      </c>
+      <c r="C801" t="inlineStr">
+        <is>
+          <t>9493202</t>
+        </is>
+      </c>
+      <c r="D801" t="inlineStr">
+        <is>
+          <t>DM-9493202/2026</t>
+        </is>
+      </c>
+      <c r="E801" t="inlineStr">
+        <is>
+          <t>AGR BOTELHO ENGENHARIA LTDA</t>
+        </is>
+      </c>
+      <c r="F801" t="n">
+        <v>1</v>
+      </c>
+      <c r="G801" t="n">
+        <v>1872</v>
+      </c>
+      <c r="H801" t="inlineStr">
+        <is>
+          <t>SERVICOS DE RECUPERACAO DE RODOVIAS</t>
+        </is>
+      </c>
+      <c r="I801" t="inlineStr"/>
+      <c r="J801" t="inlineStr"/>
+      <c r="K801" t="n">
+        <v>5107</v>
+      </c>
+      <c r="L801" t="inlineStr">
+        <is>
+          <t>EXECUCAO DE OBRAS POR CONTRATO DE BENS NAO PATRIMONIAVEIS</t>
+        </is>
+      </c>
+      <c r="M801" t="n">
+        <v>1</v>
+      </c>
+      <c r="N801" t="n">
+        <v>6305546.68</v>
+      </c>
+      <c r="O801" t="n">
+        <v>6305546.68</v>
+      </c>
+      <c r="P801" t="n">
+        <v>4557819.64</v>
+      </c>
+    </row>
+    <row r="802">
+      <c r="A802" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B802" t="inlineStr">
+        <is>
+          <t>2301762 000026/2025</t>
+        </is>
+      </c>
+      <c r="C802" t="inlineStr">
+        <is>
+          <t>9502116</t>
+        </is>
+      </c>
+      <c r="D802" t="inlineStr">
+        <is>
+          <t>DM-9502116/2026</t>
+        </is>
+      </c>
+      <c r="E802" t="inlineStr">
+        <is>
+          <t>PLANEP PLANEJAMENTO ESTUDOS E PROJETOS LTDA</t>
+        </is>
+      </c>
+      <c r="F802" t="n">
+        <v>1</v>
+      </c>
+      <c r="G802" t="n">
+        <v>8125</v>
+      </c>
+      <c r="H802" t="inlineStr">
+        <is>
+          <t>SERVICOS DE CONSULTORIA EM AREA DE ENGENHARIA CIVIL</t>
+        </is>
+      </c>
+      <c r="I802" t="inlineStr"/>
+      <c r="J802" t="inlineStr"/>
+      <c r="K802" t="n">
+        <v>3951</v>
+      </c>
+      <c r="L802" t="inlineStr">
+        <is>
+          <t>SERVICOS DE GERENCIAMENTO, SUPERVISAO E FISCALIZACAO DE OBRAS</t>
+        </is>
+      </c>
+      <c r="M802" t="n">
+        <v>1</v>
+      </c>
+      <c r="N802" t="n">
+        <v>8281446.48</v>
+      </c>
+      <c r="O802" t="n">
+        <v>0</v>
+      </c>
+      <c r="P802" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="803">
+      <c r="A803" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B803" t="inlineStr">
+        <is>
+          <t>2301762 000026/2025</t>
+        </is>
+      </c>
+      <c r="C803" t="inlineStr">
+        <is>
+          <t>9502116</t>
+        </is>
+      </c>
+      <c r="D803" t="inlineStr">
+        <is>
+          <t>DM-9502116/2026</t>
+        </is>
+      </c>
+      <c r="E803" t="inlineStr">
+        <is>
+          <t>PLANEP PLANEJAMENTO ESTUDOS E PROJETOS LTDA</t>
+        </is>
+      </c>
+      <c r="F803" t="n">
+        <v>1</v>
+      </c>
+      <c r="G803" t="n">
+        <v>8125</v>
+      </c>
+      <c r="H803" t="inlineStr">
+        <is>
+          <t>SERVICOS DE CONSULTORIA EM AREA DE ENGENHARIA CIVIL</t>
+        </is>
+      </c>
+      <c r="I803" t="inlineStr"/>
+      <c r="J803" t="inlineStr"/>
+      <c r="K803" t="n">
+        <v>5106</v>
+      </c>
+      <c r="L803" t="inlineStr">
+        <is>
+          <t>ESTUDOS E PROJETOS DE BENS NAO PATRIMONIAVEIS</t>
+        </is>
+      </c>
+      <c r="M803" t="n">
+        <v>1</v>
+      </c>
+      <c r="N803" t="n">
+        <v>8281446.48</v>
+      </c>
+      <c r="O803" t="n">
+        <v>8281446.48</v>
+      </c>
+      <c r="P803" t="n">
+        <v>5342582.88</v>
+      </c>
+    </row>
+    <row r="804">
+      <c r="A804" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B804" t="inlineStr">
+        <is>
+          <t>2301762 000027/2025</t>
+        </is>
+      </c>
+      <c r="C804" t="inlineStr">
+        <is>
+          <t>9500304</t>
+        </is>
+      </c>
+      <c r="D804" t="inlineStr">
+        <is>
+          <t>DM-9500304/2026</t>
+        </is>
+      </c>
+      <c r="E804" t="inlineStr">
+        <is>
+          <t>CONSTRUTORA CENTRO LESTE ENGENHARIA LTDA</t>
+        </is>
+      </c>
+      <c r="F804" t="n">
+        <v>1</v>
+      </c>
+      <c r="G804" t="n">
+        <v>1872</v>
+      </c>
+      <c r="H804" t="inlineStr">
+        <is>
+          <t>SERVICOS DE RECUPERACAO DE RODOVIAS</t>
+        </is>
+      </c>
+      <c r="I804" t="inlineStr"/>
+      <c r="J804" t="inlineStr"/>
+      <c r="K804" t="n">
+        <v>5107</v>
+      </c>
+      <c r="L804" t="inlineStr">
+        <is>
+          <t>EXECUCAO DE OBRAS POR CONTRATO DE BENS NAO PATRIMONIAVEIS</t>
+        </is>
+      </c>
+      <c r="M804" t="n">
+        <v>1</v>
+      </c>
+      <c r="N804" t="n">
+        <v>16936267.4</v>
+      </c>
+      <c r="O804" t="n">
+        <v>16936267.4</v>
+      </c>
+      <c r="P804" t="n">
+        <v>14124998.39</v>
+      </c>
+    </row>
+    <row r="805">
+      <c r="A805" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B805" t="inlineStr">
+        <is>
+          <t>2301762 000030/2025</t>
+        </is>
+      </c>
+      <c r="C805" t="inlineStr">
+        <is>
+          <t>9504058</t>
+        </is>
+      </c>
+      <c r="D805" t="inlineStr">
+        <is>
+          <t>DM-9504058/2026</t>
+        </is>
+      </c>
+      <c r="E805" t="inlineStr">
+        <is>
+          <t>EMCONBRAS EMPRESA DE CONSERVACAO BRASILEIRA LTDA</t>
+        </is>
+      </c>
+      <c r="F805" t="n">
+        <v>1</v>
+      </c>
+      <c r="G805" t="n">
+        <v>1872</v>
+      </c>
+      <c r="H805" t="inlineStr">
+        <is>
+          <t>SERVICOS DE RECUPERACAO DE RODOVIAS</t>
+        </is>
+      </c>
+      <c r="I805" t="inlineStr"/>
+      <c r="J805" t="inlineStr"/>
+      <c r="K805" t="n">
+        <v>5107</v>
+      </c>
+      <c r="L805" t="inlineStr">
+        <is>
+          <t>EXECUCAO DE OBRAS POR CONTRATO DE BENS NAO PATRIMONIAVEIS</t>
+        </is>
+      </c>
+      <c r="M805" t="n">
+        <v>1</v>
+      </c>
+      <c r="N805" t="n">
+        <v>28640371.76</v>
+      </c>
+      <c r="O805" t="n">
+        <v>28640371.76</v>
+      </c>
+      <c r="P805" t="n">
+        <v>19798000</v>
+      </c>
+    </row>
+    <row r="806">
+      <c r="A806" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B806" t="inlineStr">
+        <is>
+          <t>2301901 000001/2025</t>
+        </is>
+      </c>
+      <c r="C806" t="inlineStr">
+        <is>
+          <t>9493205</t>
+        </is>
+      </c>
+      <c r="D806" t="inlineStr">
+        <is>
+          <t>DO-9493205/2026-L4</t>
+        </is>
+      </c>
+      <c r="E806" t="inlineStr">
+        <is>
+          <t>FOCALLE - ENGENHARIA VIARIA LTDA.</t>
+        </is>
+      </c>
+      <c r="F806" t="n">
+        <v>1</v>
+      </c>
+      <c r="G806" t="n">
+        <v>66419</v>
+      </c>
+      <c r="H806" t="inlineStr">
+        <is>
+          <t>SERVICO DE VIGILANCIA ELETRONICA DE TRANSITO E TRAFEGO E    TRATAMENTO DAS IMAGENS</t>
+        </is>
+      </c>
+      <c r="I806" t="inlineStr"/>
+      <c r="J806" t="inlineStr"/>
+      <c r="K806" t="n">
         <v>3971</v>
       </c>
-      <c r="L799" t="inlineStr">
+      <c r="L806" t="inlineStr">
         <is>
           <t>SERVICOS TECN DE IMPLANTACAO GESTAO E ADM DO SIST DE OBSERV ELETRONICA</t>
         </is>
       </c>
-      <c r="M799" t="n">
-        <v>1</v>
-      </c>
-      <c r="N799" t="n">
+      <c r="M806" t="n">
+        <v>1</v>
+      </c>
+      <c r="N806" t="n">
         <v>64031795.21</v>
       </c>
-      <c r="O799" t="n">
+      <c r="O806" t="n">
         <v>64031795.21</v>
       </c>
-      <c r="P799" t="n">
+      <c r="P806" t="n">
         <v>31699998.96</v>
       </c>
     </row>
